--- a/safety_inspection_forms/026_preschool_classroom_safety_checklist--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/026_preschool_classroom_safety_checklist--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -835,8 +835,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -898,12 +898,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option1':_'fire_alarm_system'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option1': 'Fire Alarm System'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option2':_'working_light'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option2': 'Working Light'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option3':_'working_fire_extinguisher'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option3': 'Working Fire Extinguisher'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option1':_'working_electrical_outlet'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option1': 'Working Electrical Outlet'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option2':_'fused_outlet'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option2': 'Fused Outlet'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option3':_'extension_cord'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option3': 'Extension Cord'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option1':_'sharp_objects'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option1': 'Sharp Objects'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option2':_'heavy_furniture'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option2': 'Heavy Furniture'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option3':_'broken_glass'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option3': 'Broken Glass'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option1':_'cleaning_supplies'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option1': 'Cleaning Supplies'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option2':_'paints'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option2': 'Paints'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option3':_'chemicals'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option3': 'Chemicals'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option1':_'slippery_floors'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option1': 'Slippery Floors'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option2':_'uneven_surfaces'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option2': 'Uneven Surfaces'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option3':_'broken_glass'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option3': 'Broken Glass'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
